--- a/tiflow-diga/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DiGA.xlsx
+++ b/tiflow-diga/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DiGA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="362">
   <si>
     <t>Property</t>
   </si>
@@ -439,6 +439,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -481,10 +491,17 @@
     <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>Communication.instantiatesCanonical</t>
@@ -500,6 +517,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -541,7 +561,14 @@
     <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.basedOn.id</t>
@@ -567,16 +594,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -673,6 +690,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -751,6 +771,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -803,6 +826,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1116,7 +1142,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1505,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2443,19 +2475,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2467,7 +2499,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2481,10 +2513,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2510,16 +2542,16 @@
         <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2556,19 +2588,19 @@
         <v>76</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2580,7 +2612,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2594,10 +2626,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2620,19 +2652,19 @@
         <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2681,7 +2713,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2690,27 +2722,27 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2733,15 +2765,17 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2790,7 +2824,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2805,21 +2839,21 @@
         <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2845,13 +2879,13 @@
         <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2901,7 +2935,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2916,25 +2950,25 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2953,16 +2987,16 @@
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3012,7 +3046,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3021,27 +3055,27 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3064,13 +3098,13 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3121,7 +3155,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3142,15 +3176,15 @@
         <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3179,7 +3213,7 @@
         <v>133</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>135</v>
@@ -3220,19 +3254,19 @@
         <v>76</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3244,7 +3278,7 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>76</v>
@@ -3253,15 +3287,15 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3284,16 +3318,16 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3343,7 +3377,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3352,7 +3386,7 @@
         <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>98</v>
@@ -3369,10 +3403,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3398,13 +3432,13 @@
         <v>100</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3430,13 +3464,13 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3454,7 +3488,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3480,10 +3514,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3506,16 +3540,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3565,7 +3599,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3574,7 +3608,7 @@
         <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>98</v>
@@ -3586,15 +3620,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3617,16 +3651,16 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3676,7 +3710,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3702,14 +3736,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3728,15 +3762,17 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3785,7 +3821,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3794,27 +3830,27 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3837,15 +3873,17 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3894,7 +3932,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3903,10 +3941,10 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
@@ -3915,15 +3953,15 @@
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3949,13 +3987,13 @@
         <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3963,7 +4001,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>76</v>
@@ -3981,31 +4019,31 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>86</v>
@@ -4020,10 +4058,10 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4031,14 +4069,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4057,16 +4095,16 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4092,31 +4130,31 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4125,27 +4163,27 @@
         <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4168,16 +4206,16 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4203,13 +4241,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4227,7 +4265,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4236,7 +4274,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>98</v>
@@ -4245,18 +4283,18 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4282,20 +4320,20 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="R26" t="s" s="2">
         <v>76</v>
@@ -4316,13 +4354,13 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -4340,7 +4378,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4358,7 +4396,7 @@
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4366,10 +4404,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4392,15 +4430,17 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4425,13 +4465,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4449,7 +4489,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4458,7 +4498,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
@@ -4470,19 +4510,19 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4501,15 +4541,17 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4558,7 +4600,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4567,27 +4609,27 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4610,16 +4652,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4645,13 +4687,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4669,7 +4711,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4678,7 +4720,7 @@
         <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>98</v>
@@ -4687,18 +4729,18 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4721,16 +4763,16 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4780,7 +4822,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4789,27 +4831,27 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4832,16 +4874,16 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4891,7 +4933,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4900,27 +4942,27 @@
         <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4943,16 +4985,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5002,7 +5044,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5017,10 +5059,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5028,10 +5070,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5054,16 +5096,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5113,7 +5155,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5128,10 +5170,10 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5139,10 +5181,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5165,16 +5207,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5224,7 +5266,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5233,27 +5275,27 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5276,13 +5318,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5333,7 +5375,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5354,15 +5396,15 @@
         <v>76</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5391,7 +5433,7 @@
         <v>133</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>135</v>
@@ -5432,19 +5474,19 @@
         <v>76</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5456,7 +5498,7 @@
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>76</v>
@@ -5465,15 +5507,15 @@
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5496,16 +5538,16 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5555,7 +5597,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5564,7 +5606,7 @@
         <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>98</v>
@@ -5581,10 +5623,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5610,13 +5652,13 @@
         <v>100</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5642,13 +5684,13 @@
         <v>76</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>76</v>
@@ -5666,7 +5708,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5692,10 +5734,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5718,16 +5760,16 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5777,7 +5819,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5786,7 +5828,7 @@
         <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>98</v>
@@ -5798,15 +5840,15 @@
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5829,16 +5871,16 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5888,7 +5930,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5914,10 +5956,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5940,16 +5982,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5999,7 +6041,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6008,27 +6050,27 @@
         <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6051,13 +6093,13 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6108,7 +6150,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6129,15 +6171,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6166,7 +6208,7 @@
         <v>133</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>135</v>
@@ -6207,19 +6249,19 @@
         <v>76</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6231,7 +6273,7 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
@@ -6240,15 +6282,15 @@
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6271,16 +6313,16 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6330,7 +6372,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6339,7 +6381,7 @@
         <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>98</v>
@@ -6356,10 +6398,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6385,13 +6427,13 @@
         <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6417,13 +6459,13 @@
         <v>76</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>76</v>
@@ -6441,7 +6483,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6467,10 +6509,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6493,16 +6535,16 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6552,7 +6594,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6561,7 +6603,7 @@
         <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>98</v>
@@ -6573,15 +6615,15 @@
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6604,16 +6646,16 @@
         <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6663,7 +6705,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6689,10 +6731,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6715,16 +6757,16 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6750,13 +6792,13 @@
         <v>76</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -6774,7 +6816,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6783,27 +6825,27 @@
         <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6826,15 +6868,17 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -6883,7 +6927,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6892,27 +6936,27 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6935,13 +6979,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6992,7 +7036,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7001,7 +7045,7 @@
         <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>98</v>
@@ -7013,15 +7057,15 @@
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>76</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7044,13 +7088,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7101,7 +7145,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7122,15 +7166,15 @@
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7159,7 +7203,7 @@
         <v>133</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>135</v>
@@ -7200,19 +7244,19 @@
         <v>76</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7224,7 +7268,7 @@
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
@@ -7233,19 +7277,19 @@
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7267,16 +7311,16 @@
         <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7325,7 +7369,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7337,7 +7381,7 @@
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>76</v>
@@ -7351,10 +7395,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7377,16 +7421,16 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7436,7 +7480,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>86</v>
@@ -7445,7 +7489,7 @@
         <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>98</v>
@@ -7457,15 +7501,15 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>76</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7488,15 +7532,17 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7545,7 +7591,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7554,19 +7600,19 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>76</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-diga/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DiGA.xlsx
+++ b/tiflow-diga/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DiGA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="352">
   <si>
     <t>Property</t>
   </si>
@@ -439,6 +439,136 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Communication.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Communication.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Unique identifier</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this communication by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Communication.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Instantiates FHIR protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>Communication.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Instantiates external protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Communication.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fulfills
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Task) &lt;&lt;referenced&gt;&gt;
+</t>
+  </si>
+  <si>
+    <t>Gibt das E-Rezept-Token gemäß gemSpec_DM_eRp an.</t>
+  </si>
+  <si>
+    <t>An order, proposal or plan fulfilled in whole or in part by this Communication.</t>
+  </si>
+  <si>
+    <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>Communication.basedOn.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Communication.basedOn.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -447,153 +577,6 @@
   </si>
   <si>
     <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Communication.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Communication.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Unique identifier</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this communication by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
-    <t>Communication.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
-  </si>
-  <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
-    <t>Event.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=DEFN].target</t>
-  </si>
-  <si>
-    <t>Communication.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Instantiates external protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
-  </si>
-  <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Communication.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fulfills
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Task) &lt;&lt;referenced&gt;&gt;
-</t>
-  </si>
-  <si>
-    <t>Gibt das E-Rezept-Token gemäß gemSpec_DM_eRp an.</t>
-  </si>
-  <si>
-    <t>An order, proposal or plan fulfilled in whole or in part by this Communication.</t>
-  </si>
-  <si>
-    <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
-    <t>Communication.basedOn.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Communication.basedOn.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -690,9 +673,6 @@
     <t>Part of this action.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -771,9 +751,6 @@
     <t>Event.statusReason</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -826,9 +803,6 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1142,13 +1116,7 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>Event.note</t>
-  </si>
-  <si>
-    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1473,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2475,19 +2443,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2499,7 +2467,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2513,10 +2481,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2542,16 +2510,16 @@
         <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2588,19 +2556,19 @@
         <v>76</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2612,7 +2580,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2626,10 +2594,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2652,19 +2620,19 @@
         <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2713,7 +2681,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2722,27 +2690,27 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2765,17 +2733,15 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -2824,7 +2790,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2839,21 +2805,21 @@
         <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2879,13 +2845,13 @@
         <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2935,7 +2901,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2950,25 +2916,25 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2987,16 +2953,16 @@
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3046,7 +3012,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3055,27 +3021,27 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3098,13 +3064,13 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3155,7 +3121,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3176,15 +3142,15 @@
         <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3213,7 +3179,7 @@
         <v>133</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>135</v>
@@ -3254,19 +3220,19 @@
         <v>76</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3278,7 +3244,7 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>76</v>
@@ -3287,15 +3253,15 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3318,16 +3284,16 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3377,7 +3343,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3386,7 +3352,7 @@
         <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>98</v>
@@ -3403,10 +3369,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3432,13 +3398,13 @@
         <v>100</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3464,13 +3430,13 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3488,7 +3454,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3514,10 +3480,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3540,16 +3506,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3599,7 +3565,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3608,7 +3574,7 @@
         <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>98</v>
@@ -3620,15 +3586,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3651,16 +3617,16 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3710,7 +3676,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3736,14 +3702,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3762,17 +3728,15 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3821,7 +3785,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3830,27 +3794,27 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3873,17 +3837,15 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3932,7 +3894,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3941,10 +3903,10 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
@@ -3953,15 +3915,15 @@
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3987,13 +3949,13 @@
         <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4001,7 +3963,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>76</v>
@@ -4019,13 +3981,13 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>76</v>
@@ -4043,7 +4005,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>86</v>
@@ -4058,10 +4020,10 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4069,14 +4031,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4095,16 +4057,16 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4130,13 +4092,13 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4154,7 +4116,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4163,27 +4125,27 @@
         <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4206,16 +4168,16 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4241,13 +4203,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4265,7 +4227,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4274,7 +4236,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>98</v>
@@ -4283,18 +4245,18 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4320,20 +4282,20 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="R26" t="s" s="2">
         <v>76</v>
@@ -4354,13 +4316,13 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -4378,7 +4340,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4396,7 +4358,7 @@
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4404,10 +4366,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4430,17 +4392,15 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4465,13 +4425,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4489,7 +4449,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4498,7 +4458,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
@@ -4510,19 +4470,19 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4541,17 +4501,15 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4600,7 +4558,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4609,27 +4567,27 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4652,16 +4610,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4687,13 +4645,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4711,7 +4669,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4720,7 +4678,7 @@
         <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>98</v>
@@ -4729,18 +4687,18 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4763,16 +4721,16 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4822,7 +4780,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4831,27 +4789,27 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4874,16 +4832,16 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4933,7 +4891,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4942,27 +4900,27 @@
         <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4985,16 +4943,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5044,7 +5002,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5059,10 +5017,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5070,10 +5028,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5096,16 +5054,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>295</v>
-      </c>
       <c r="N33" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5155,7 +5113,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5170,10 +5128,10 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5181,10 +5139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5207,16 +5165,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5266,7 +5224,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5275,27 +5233,27 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5318,13 +5276,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5375,7 +5333,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5396,15 +5354,15 @@
         <v>76</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5433,7 +5391,7 @@
         <v>133</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>135</v>
@@ -5474,19 +5432,19 @@
         <v>76</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5498,7 +5456,7 @@
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>76</v>
@@ -5507,15 +5465,15 @@
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5538,16 +5496,16 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5597,7 +5555,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5606,7 +5564,7 @@
         <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>98</v>
@@ -5623,10 +5581,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5652,13 +5610,13 @@
         <v>100</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5684,13 +5642,13 @@
         <v>76</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>76</v>
@@ -5708,7 +5666,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5734,10 +5692,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5760,16 +5718,16 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5819,7 +5777,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5828,7 +5786,7 @@
         <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>98</v>
@@ -5840,15 +5798,15 @@
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5871,16 +5829,16 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5930,7 +5888,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5956,10 +5914,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5982,16 +5940,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6041,7 +5999,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6050,27 +6008,27 @@
         <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6093,13 +6051,13 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6150,7 +6108,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6171,15 +6129,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6208,7 +6166,7 @@
         <v>133</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>135</v>
@@ -6249,19 +6207,19 @@
         <v>76</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6273,7 +6231,7 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
@@ -6282,15 +6240,15 @@
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6313,16 +6271,16 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6372,7 +6330,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6381,7 +6339,7 @@
         <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>98</v>
@@ -6398,10 +6356,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6427,13 +6385,13 @@
         <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6459,13 +6417,13 @@
         <v>76</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>76</v>
@@ -6483,7 +6441,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6509,10 +6467,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6535,16 +6493,16 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6594,7 +6552,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6603,7 +6561,7 @@
         <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>98</v>
@@ -6615,15 +6573,15 @@
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6646,16 +6604,16 @@
         <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6705,7 +6663,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6731,10 +6689,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6757,16 +6715,16 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6792,13 +6750,13 @@
         <v>76</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -6816,7 +6774,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6825,27 +6783,27 @@
         <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6868,17 +6826,15 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -6927,7 +6883,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6936,27 +6892,27 @@
         <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6979,13 +6935,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7036,7 +6992,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7045,7 +7001,7 @@
         <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>98</v>
@@ -7057,15 +7013,15 @@
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>182</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7088,13 +7044,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7145,7 +7101,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7166,15 +7122,15 @@
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7203,7 +7159,7 @@
         <v>133</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>135</v>
@@ -7244,19 +7200,19 @@
         <v>76</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7268,7 +7224,7 @@
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
@@ -7277,19 +7233,19 @@
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7311,16 +7267,16 @@
         <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7369,7 +7325,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7381,7 +7337,7 @@
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>76</v>
@@ -7395,10 +7351,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7421,16 +7377,16 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7480,7 +7436,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>86</v>
@@ -7489,7 +7445,7 @@
         <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>98</v>
@@ -7501,15 +7457,15 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>182</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7532,17 +7488,15 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7591,7 +7545,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7600,19 +7554,19 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>361</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
